--- a/Design/Excel/ET/Datas/Game/UI.xlsx
+++ b/Design/Excel/ET/Datas/Game/UI.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17800"/>
+    <workbookView windowHeight="17200"/>
   </bookViews>
   <sheets>
     <sheet name="UI界面" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0" calcOnSave="0" fullPrecision="0" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -149,40 +149,22 @@
     <t>LockStep/UILSRoom</t>
   </si>
   <si>
-    <t>DialogForm</t>
-  </si>
-  <si>
-    <t>弹出框</t>
-  </si>
-  <si>
-    <t>Hot/DialogForm</t>
-  </si>
-  <si>
-    <t>MenuForm</t>
-  </si>
-  <si>
-    <t>主菜单</t>
-  </si>
-  <si>
-    <t>Hot/MenuForm</t>
-  </si>
-  <si>
-    <t>SettingForm</t>
-  </si>
-  <si>
-    <t>设置</t>
-  </si>
-  <si>
-    <t>Hot/SettingForm</t>
-  </si>
-  <si>
-    <t>AboutForm</t>
-  </si>
-  <si>
-    <t>关于</t>
-  </si>
-  <si>
-    <t>Hot/AboutForm</t>
+    <t>SurvivorLobby</t>
+  </si>
+  <si>
+    <t>联机幸存者加房界面</t>
+  </si>
+  <si>
+    <t>SurvivorOnline/Lobby</t>
+  </si>
+  <si>
+    <t>SurvivorHud</t>
+  </si>
+  <si>
+    <t>联机幸存者局内界面</t>
+  </si>
+  <si>
+    <t>SurvivorOnline/Hud</t>
   </si>
 </sst>
 </file>
@@ -195,7 +177,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,7 +190,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -216,14 +198,14 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -239,7 +221,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -270,7 +252,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -278,7 +260,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -286,7 +268,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -294,14 +276,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -309,42 +291,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -650,149 +625,149 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1155,7 +1130,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="8.87272727272727" style="1"/>
@@ -1387,7 +1362,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="B10" s="3">
-        <v>1</v>
+        <v>9801</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>40</v>
@@ -1402,15 +1377,15 @@
         <v>32</v>
       </c>
       <c r="G10" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="B11" s="3">
-        <v>100</v>
+        <v>9802</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>43</v>
@@ -1422,64 +1397,18 @@
         <v>45</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G11" s="3" t="b">
         <v>0</v>
       </c>
       <c r="H11" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="B12" s="3">
-        <v>101</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="B13" s="3">
-        <v>102</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/Design/Excel/ET/Datas/Game/UI.xlsx
+++ b/Design/Excel/ET/Datas/Game/UI.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr autoCompressPictures="1"/>
   <bookViews>
     <workbookView windowHeight="17200"/>
   </bookViews>
   <sheets>
     <sheet name="UI界面" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0" calcOnSave="0" fullPrecision="0" concurrentCalc="0"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" fullPrecision="0" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
+    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures">
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
@@ -27,150 +27,186 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>CSName</t>
-  </si>
-  <si>
-    <t>Desc</t>
-  </si>
-  <si>
-    <t>AssetName</t>
-  </si>
-  <si>
-    <t>UIGroupName</t>
-  </si>
-  <si>
-    <t>AllowMultiInstance</t>
-  </si>
-  <si>
-    <t>PauseCoveredUIForm</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string&amp;group=ge</t>
-  </si>
-  <si>
-    <t>string#path=normal;UI/UIForm/*.prefab</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>界面编号</t>
-  </si>
-  <si>
-    <t>代码名（程序填）</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>资源名称</t>
-  </si>
-  <si>
-    <t>界面组名称</t>
-  </si>
-  <si>
-    <t>是否允许多个界面实例</t>
-  </si>
-  <si>
-    <t>是否暂停被其覆盖的界面</t>
-  </si>
-  <si>
-    <t>UIHelp</t>
-  </si>
-  <si>
-    <t>帮助界面</t>
-  </si>
-  <si>
-    <t>Demo/UIHelp</t>
-  </si>
-  <si>
-    <t>Pop</t>
-  </si>
-  <si>
-    <t>UILobby</t>
-  </si>
-  <si>
-    <t>大厅面</t>
-  </si>
-  <si>
-    <t>Demo/UILobby</t>
-  </si>
-  <si>
-    <t>UILogin</t>
-  </si>
-  <si>
-    <t>登录界面</t>
-  </si>
-  <si>
-    <t>Demo/UILogin</t>
-  </si>
-  <si>
-    <t>Default</t>
-  </si>
-  <si>
-    <t>UILSLogin</t>
-  </si>
-  <si>
-    <t>LockStep/UILSLogin</t>
-  </si>
-  <si>
-    <t>UILSLobby</t>
-  </si>
-  <si>
-    <t>LockStep/UILSLobby</t>
-  </si>
-  <si>
-    <t>UILSRoom</t>
-  </si>
-  <si>
-    <t>房间界面</t>
-  </si>
-  <si>
-    <t>LockStep/UILSRoom</t>
-  </si>
-  <si>
-    <t>SurvivorLobby</t>
-  </si>
-  <si>
-    <t>联机幸存者加房界面</t>
-  </si>
-  <si>
-    <t>SurvivorOnline/Lobby</t>
-  </si>
-  <si>
-    <t>SurvivorHud</t>
-  </si>
-  <si>
-    <t>联机幸存者局内界面</t>
-  </si>
-  <si>
-    <t>SurvivorOnline/Hud</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="58">
+  <si>
+    <t xml:space="preserve">##var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AssetName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UIGroupName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllowMultiInstance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PauseCoveredUIForm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string&amp;group=ge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string#path=normal;UI/UIForm/*.prefab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##</t>
+  </si>
+  <si>
+    <t xml:space="preserve">界面编号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">代码名（程序填）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">备注</t>
+  </si>
+  <si>
+    <t xml:space="preserve">资源名称</t>
+  </si>
+  <si>
+    <t xml:space="preserve">界面组名称</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是否允许多个界面实例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是否暂停被其覆盖的界面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UIHelp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">帮助界面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demo/UIHelp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UILobby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大厅面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demo/UILobby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UILogin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">登录界面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demo/UILogin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UILSLogin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LockStep/UILSLogin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UILSLobby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LockStep/UILSLobby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UILSRoom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">房间界面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LockStep/UILSRoom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SurvivorLobby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">联机幸存者加房界面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SurvivorOnline/Lobby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SurvivorHud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">联机幸存者局内界面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SurvivorOnline/Hud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SurvivorOnline/SurvivorLobby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SurvivorOnline/SurvivorHud</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SurvivorLogin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">联机幸存者登录界面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SurvivorOnline/SurvivorLogin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SurvivorSkillChoice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">联机幸存者升级技能三选一界面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SurvivorOnline/SurvivorSkillChoice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SurvivorGameOver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">联机幸存者游戏结束界面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SurvivorOnline/SurvivorGameOver</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -186,7 +222,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
@@ -194,7 +230,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
@@ -625,154 +661,154 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" xfId="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -836,8 +872,8 @@
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1128,7 +1164,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr/>
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14" outlineLevelCol="7"/>
@@ -1371,7 +1407,7 @@
         <v>41</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>32</v>
@@ -1394,7 +1430,7 @@
         <v>44</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>25</v>
@@ -1406,7 +1442,77 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12" ht="14" customHeight="1">
+      <c r="B12" s="3">
+        <v>9800</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="3">
+        <v>9803</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3">
+        <v>9804</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetCalcPr fullCalcOnLoad="1"/>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
   <headerFooter/>
